--- a/artfynd/A 64302-2021 artfynd.xlsx
+++ b/artfynd/A 64302-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 64302-2021 artfynd.xlsx
+++ b/artfynd/A 64302-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>107079130</v>
+        <v>130741320</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nästsjön öst tångeråsen, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444450.7944263208</v>
+        <v>444326</v>
       </c>
       <c r="R2" t="n">
-        <v>7053630.048768651</v>
+        <v>7053588</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-03-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-03-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>107079126</v>
+        <v>107079120</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444413.4365126948</v>
+        <v>444412</v>
       </c>
       <c r="R3" t="n">
-        <v>7053583.527588004</v>
+        <v>7053582</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-03-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,12 +872,7 @@
         <v>107079121</v>
       </c>
       <c r="B4" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444453.8194740729</v>
+        <v>444454</v>
       </c>
       <c r="R4" t="n">
-        <v>7053624.655194082</v>
+        <v>7053625</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-03-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>107079120</v>
+        <v>107079137</v>
       </c>
       <c r="B5" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444412.5220976253</v>
+        <v>444450</v>
       </c>
       <c r="R5" t="n">
-        <v>7053582.208442768</v>
+        <v>7053625</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,14 @@
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>måttligt - rikligt i området</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,19 +1068,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>107079137</v>
+        <v>113995171</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1157,16 +1097,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nästsjön öst tångeråsen, Jmt</t>
+          <t>Nästsjön ö tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444449.8099155131</v>
+        <v>444428</v>
       </c>
       <c r="R6" t="n">
-        <v>7053624.72540946</v>
+        <v>7053708</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,27 +1136,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-03-01</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-01-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-03-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-01-09</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>måttligt - rikligt i området</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,6 +1155,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1240,50 +1174,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>107079129</v>
+        <v>130734188</v>
       </c>
       <c r="B7" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nästsjön öst tångeråsen, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444427.368497182</v>
+        <v>444304</v>
       </c>
       <c r="R7" t="n">
-        <v>7053666.507922567</v>
+        <v>7053564</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,22 +1242,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-03-01</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-03-01</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Växer på en tydligt gammal gran i relativt senvuxen gles granskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,72 +1261,92 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113995206</v>
+        <v>130734191</v>
       </c>
       <c r="B8" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nästsjön ö tångeråsen, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444433</v>
+        <v>444407</v>
       </c>
       <c r="R8" t="n">
-        <v>7053674</v>
+        <v>7053726</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,17 +1373,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>Relativt rikligt med garnlav på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1445,37 +1392,63 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113995171</v>
+        <v>130734192</v>
       </c>
       <c r="B9" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1502,14 +1475,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nästsjön ö tångeråsen, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444428</v>
+        <v>444423</v>
       </c>
       <c r="R9" t="n">
-        <v>7053708</v>
+        <v>7053773</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,17 +1509,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>Måttligt till rikligt med garnlavsbålar på flera granar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,18 +1532,547 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130741319</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>nästsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>444417</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7053741</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Benny Öwre</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Benny Öwre</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>107079126</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Nästsjön öst tångeråsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>444413</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7053583</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-03-01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-03-01</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>107079129</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Nästsjön öst tångeråsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>444428</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7053666</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-03-01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-03-01</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>107079130</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Nästsjön öst tångeråsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>444451</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7053630</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-03-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-03-01</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>113995206</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Nästsjön ö tångeråsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>444433</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7053674</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-01-09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-01-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 64302-2021 artfynd.xlsx
+++ b/artfynd/A 64302-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130741320</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107079120</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107079121</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107079137</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1171,6 +1196,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113995171</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,6 +1332,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734188</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1438,6 +1473,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734191</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1574,6 +1614,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734192</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1676,6 +1721,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130741319</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1773,6 +1823,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107079126</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1870,6 +1925,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107079129</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1967,6 +2027,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107079130</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2073,8 +2138,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113995206</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>